--- a/reports/member_funnel/downloads/member_funnel_7d_target_vip.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_target_vip.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>veritaskm</t>
+          <t>kk_2905067716</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01084555847</t>
+          <t>01099172715</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EDM_0220</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudan Pro 3L Shell</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_2905067716</t>
+          <t>kk_4201213646</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01099172715</t>
+          <t>01027969918</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_ECOM_cart_sale</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>Cove Beach Pant</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1039,12 +1039,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3215602159</t>
+          <t>kk_2933318514</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01050406700</t>
+          <t>01048004176</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CSC1938 Dually Mountain Outerchange</t>
+          <t>Centrillium 2.5L Jacket</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1071,27 +1071,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_2933318514</t>
+          <t>kk_4548582000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01048004176</t>
+          <t>01099254539</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Centrillium 2.5L Jacket</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1103,12 +1103,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_4548582000</t>
+          <t>kk_4614369618</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01099254539</t>
+          <t>01093720985</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>M's Stone Dash Fleece Jacket</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1135,27 +1135,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4614369618</t>
+          <t>jsy3689</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01093720985</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>M's Stone Dash Fleece Jacket</t>
+          <t>Acker Rock Twill SS Button Down</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1167,27 +1167,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jsy3689</t>
+          <t>idlsb</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01031293827</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Acker Rock Twill SS Button Down</t>
+          <t>M's Cow Mountain Cargo Straight Pants</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1199,12 +1199,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>idlsb</t>
+          <t>swsga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01031293827</t>
+          <t>01090067664</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>M's Cow Mountain Cargo Straight Pants</t>
+          <t>M's 365 Mountain II Shirts Jacket</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1231,12 +1231,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>swsga</t>
+          <t>insoule1201</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01090067664</t>
+          <t>01024461707</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>M's 365 Mountain II Shirts Jacket</t>
+          <t>Centrillium Jacket</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1263,12 +1263,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>insoule1201</t>
+          <t>rnjsrldn135</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01024461707</t>
+          <t>01033756034</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Centrillium Jacket</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rnjsrldn135</t>
+          <t>kk_4787402711</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01033756034</t>
+          <t>01022018682</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>M's Lee Hike Jacket</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4787402711</t>
+          <t>kk_3876211678</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01022018682</t>
+          <t>01038900880</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>M's Lee Hike Jacket</t>
+          <t>Centrillium II Jacket</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_3876211678</t>
+          <t>kk_4830354827</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01038900880</t>
+          <t>01058470790</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Centrillium II Jacket</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1391,27 +1391,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4830354827</t>
+          <t>likjky1207</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01058470790</t>
+          <t>01028547812</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>KONOS TRILLIUM ATR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>likjky1207</t>
+          <t>hee615</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01028547812</t>
+          <t>01077099356</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KONOS TRILLIUM ATR</t>
+          <t>Castle Rock 20L Backpack II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1455,27 +1455,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hee615</t>
+          <t>rokmc8375</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01077099356</t>
+          <t>01033942995</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Castle Rock 20L Backpack II</t>
+          <t>M's Tonto Dome Detachable Down Jacket</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1487,27 +1487,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>rokmc8375</t>
+          <t>jhmun150102</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01033942995</t>
+          <t>01029758998</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>M's Tonto Dome Detachable Down Jacket</t>
+          <t>M's Dana Cove OFZ ICE Straight Pants</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1519,27 +1519,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>jhmun150102</t>
+          <t>camino</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01029758998</t>
+          <t>01099009610</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>M's Dana Cove OFZ ICE Straight Pants</t>
+          <t>W's Cow Mountain 2L Jacket</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>camino</t>
+          <t>bulls3005</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01099009610</t>
+          <t>01030830402</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>W's Cow Mountain 2L Jacket</t>
+          <t>KONOS TRILLIUM ATR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1583,27 +1583,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bulls3005</t>
+          <t>kk_4563468909</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01030830402</t>
+          <t>01050047528</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KONOS TRILLIUM ATR</t>
+          <t>ESCAPE THRIVE TITANIUM MID OUTDRY</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1615,27 +1615,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4563468909</t>
+          <t>bluewolf</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01050047528</t>
+          <t>01022741671</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ESCAPE THRIVE TITANIUM MID OUTDRY</t>
+          <t>Silver Ridge 3.0 LS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1647,12 +1647,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bluewolf</t>
+          <t>kk_4738944549</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01022741671</t>
+          <t>01077475609</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Silver Ridge 3.0 LS</t>
+          <t>W’s 365 Mountain II Pants</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1679,62 +1679,30 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4738944549</t>
+          <t>nudyrody</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01077475609</t>
+          <t>01054493261</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>W’s 365 Mountain II Pants</t>
+          <t>Street Transit III Backpack</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
-        <is>
-          <t>VIP_EXCLUSIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>nudyrody</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>01054493261</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Street Transit III Backpack</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
         <is>
           <t>VIP_EXCLUSIVE</t>
         </is>
